--- a/corona-server-side-asp.net/Excels/Sections/מבט על/נפטרים מצטבר.xlsx
+++ b/corona-server-side-asp.net/Excels/Sections/מבט על/נפטרים מצטבר.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>key</t>
   </si>
@@ -28,6 +28,9 @@
   </si>
   <si>
     <t>group</t>
+  </si>
+  <si>
+    <t>keyEnglish</t>
   </si>
 </sst>
 </file>
@@ -71,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -82,6 +85,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -366,18 +370,21 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C2" s="3">
+      <c r="D2" s="3">
         <v>13171</v>
       </c>
     </row>
@@ -395,6 +402,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>